--- a/diseases/d107/1995-1999.xlsx
+++ b/diseases/d107/1995-1999.xlsx
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11393,7 +11393,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -16193,7 +16193,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16993,7 +16993,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17793,7 +17793,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18593,7 +18593,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -20728,7 +20728,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -21673,7 +21673,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22618,7 +22618,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -23563,7 +23563,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24508,7 +24508,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -25453,7 +25453,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26398,7 +26398,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -27343,7 +27343,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28288,7 +28288,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -29233,7 +29233,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30178,7 +30178,7 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN152" t="b">
@@ -31123,7 +31123,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32458,7 +32458,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -33403,7 +33403,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -34348,7 +34348,7 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN174" t="b">
@@ -35293,7 +35293,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -36238,7 +36238,7 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN184" t="b">
@@ -37183,7 +37183,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -38128,7 +38128,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -39073,7 +39073,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -40018,7 +40018,7 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -40963,7 +40963,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -41908,7 +41908,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -42853,7 +42853,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -44427,7 +44427,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -45372,7 +45372,7 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN232" t="b">
@@ -46317,7 +46317,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -47262,7 +47262,7 @@
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN242" t="b">
@@ -48207,7 +48207,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -49152,7 +49152,7 @@
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN252" t="b">
@@ -50097,7 +50097,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -51042,7 +51042,7 @@
       </c>
       <c r="AM262" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN262" t="b">
@@ -51987,7 +51987,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -52932,7 +52932,7 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN272" t="b">
@@ -53877,7 +53877,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -54822,7 +54822,7 @@
       </c>
       <c r="AM282" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN282" t="b">

--- a/diseases/d107/1995-1999.xlsx
+++ b/diseases/d107/1995-1999.xlsx
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11393,7 +11393,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -16193,7 +16193,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16993,7 +16993,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17793,7 +17793,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18593,7 +18593,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -20343,6 +20343,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20728,7 +20733,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -21288,6 +21293,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21673,7 +21683,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22233,6 +22243,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22618,7 +22633,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -23178,6 +23193,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23563,7 +23583,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24123,6 +24143,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24508,7 +24533,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -25068,6 +25093,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25453,7 +25483,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26013,6 +26043,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26398,7 +26433,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -26958,6 +26993,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27343,7 +27383,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27903,6 +27943,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28288,7 +28333,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -28848,6 +28893,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29233,7 +29283,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -29793,6 +29843,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30178,7 +30233,7 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN152" t="b">
@@ -30738,6 +30793,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31123,7 +31183,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32073,6 +32133,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32458,7 +32523,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -33018,6 +33083,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33403,7 +33473,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -33963,6 +34033,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34348,7 +34423,7 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN174" t="b">
@@ -34908,6 +34983,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35293,7 +35373,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -35853,6 +35933,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36238,7 +36323,7 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN184" t="b">
@@ -36798,6 +36883,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37183,7 +37273,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -37743,6 +37833,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38128,7 +38223,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -38688,6 +38783,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39073,7 +39173,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -39633,6 +39733,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40018,7 +40123,7 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -40578,6 +40683,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40963,7 +41073,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -41523,6 +41633,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41908,7 +42023,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -42468,6 +42583,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42853,7 +42973,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -43803,6 +43923,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44427,7 +44552,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -44987,6 +45112,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45372,7 +45502,7 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN232" t="b">
@@ -45932,6 +46062,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46317,7 +46452,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -46877,6 +47012,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47262,7 +47402,7 @@
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN242" t="b">
@@ -47822,6 +47962,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48207,7 +48352,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -48767,6 +48912,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49152,7 +49302,7 @@
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN252" t="b">
@@ -49712,6 +49862,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50097,7 +50252,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -50657,6 +50812,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51042,7 +51202,7 @@
       </c>
       <c r="AM262" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN262" t="b">
@@ -51602,6 +51762,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51987,7 +52152,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -52547,6 +52712,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52932,7 +53102,7 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN272" t="b">
@@ -53492,6 +53662,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53877,7 +54052,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -54437,6 +54612,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54822,7 +55002,7 @@
       </c>
       <c r="AM282" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN282" t="b">

--- a/diseases/d107/1995-1999.xlsx
+++ b/diseases/d107/1995-1999.xlsx
@@ -20338,6 +20338,11 @@
       <c r="Q100" t="n">
         <v>0</v>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20350,13 +20355,23 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
       </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV100" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -21273,6 +21288,11 @@
       <c r="Q105" t="n">
         <v>0</v>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21285,13 +21305,23 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
       </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV105" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -22208,6 +22238,11 @@
       <c r="Q110" t="n">
         <v>0</v>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22220,13 +22255,23 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
       </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV110" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -23143,6 +23188,11 @@
       <c r="Q115" t="n">
         <v>0</v>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23155,13 +23205,23 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
       </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV115" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -24078,6 +24138,11 @@
       <c r="Q120" t="n">
         <v>0</v>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24090,13 +24155,23 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
       </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV120" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -25013,6 +25088,11 @@
       <c r="Q125" t="n">
         <v>0</v>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25025,13 +25105,23 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
       </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV125" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -25948,6 +26038,11 @@
       <c r="Q130" t="n">
         <v>0</v>
       </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25960,13 +26055,23 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
         <v>0</v>
       </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV130" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -26883,6 +26988,11 @@
       <c r="Q135" t="n">
         <v>0</v>
       </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26895,13 +27005,23 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
       </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV135" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -27818,6 +27938,11 @@
       <c r="Q140" t="n">
         <v>0</v>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27830,13 +27955,23 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
       </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV140" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -28753,6 +28888,11 @@
       <c r="Q145" t="n">
         <v>0</v>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28765,13 +28905,23 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
       </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV145" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -29688,6 +29838,11 @@
       <c r="Q150" t="n">
         <v>0</v>
       </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29700,13 +29855,23 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
       </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV150" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -30623,6 +30788,11 @@
       <c r="Q155" t="n">
         <v>0</v>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30635,13 +30805,23 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
       </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV155" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -31948,6 +32128,11 @@
       <c r="Q162" t="n">
         <v>0</v>
       </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31960,13 +32145,23 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
         <v>0</v>
       </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV162" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -32883,6 +33078,11 @@
       <c r="Q167" t="n">
         <v>0</v>
       </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32895,13 +33095,23 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
       </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV167" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -33818,6 +34028,11 @@
       <c r="Q172" t="n">
         <v>0</v>
       </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33830,13 +34045,23 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
       </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV172" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -34753,6 +34978,11 @@
       <c r="Q177" t="n">
         <v>0</v>
       </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34765,13 +34995,23 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
         <v>0</v>
       </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV177" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -35688,6 +35928,11 @@
       <c r="Q182" t="n">
         <v>0</v>
       </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35700,13 +35945,23 @@
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr"/>
       <c r="AT182" t="n">
         <v>0</v>
       </c>
+      <c r="AU182" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV182" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -36623,6 +36878,11 @@
       <c r="Q187" t="n">
         <v>0</v>
       </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36635,13 +36895,23 @@
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="n">
         <v>0</v>
       </c>
+      <c r="AU187" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV187" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -37558,6 +37828,11 @@
       <c r="Q192" t="n">
         <v>0</v>
       </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37570,13 +37845,23 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
         <v>0</v>
       </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV192" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -38493,6 +38778,11 @@
       <c r="Q197" t="n">
         <v>0</v>
       </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -38505,13 +38795,23 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS197" t="inlineStr"/>
       <c r="AT197" t="n">
         <v>0</v>
       </c>
+      <c r="AU197" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV197" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -39428,6 +39728,11 @@
       <c r="Q202" t="n">
         <v>0</v>
       </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39440,13 +39745,23 @@
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS202" t="inlineStr"/>
       <c r="AT202" t="n">
         <v>0</v>
       </c>
+      <c r="AU202" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV202" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -40363,6 +40678,11 @@
       <c r="Q207" t="n">
         <v>0</v>
       </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40375,13 +40695,23 @@
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr"/>
       <c r="AT207" t="n">
         <v>0</v>
       </c>
+      <c r="AU207" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV207" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -41298,6 +41628,11 @@
       <c r="Q212" t="n">
         <v>0</v>
       </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -41310,13 +41645,23 @@
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr"/>
       <c r="AT212" t="n">
         <v>0</v>
       </c>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV212" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -42233,6 +42578,11 @@
       <c r="Q217" t="n">
         <v>0</v>
       </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA217" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42245,13 +42595,23 @@
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR217" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr"/>
       <c r="AT217" t="n">
         <v>0</v>
       </c>
+      <c r="AU217" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV217" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -43558,6 +43918,11 @@
       <c r="Q224" t="n">
         <v>0</v>
       </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -43570,13 +43935,23 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr"/>
       <c r="AT224" t="n">
         <v>0</v>
       </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV224" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -44732,6 +45107,11 @@
       <c r="Q230" t="n">
         <v>0</v>
       </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -44744,13 +45124,23 @@
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr"/>
       <c r="AT230" t="n">
         <v>0</v>
       </c>
+      <c r="AU230" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV230" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -45667,6 +46057,11 @@
       <c r="Q235" t="n">
         <v>0</v>
       </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -45679,13 +46074,23 @@
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR235" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS235" t="inlineStr"/>
       <c r="AT235" t="n">
         <v>0</v>
       </c>
+      <c r="AU235" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV235" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -46602,6 +47007,11 @@
       <c r="Q240" t="n">
         <v>0</v>
       </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46614,13 +47024,23 @@
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS240" t="inlineStr"/>
       <c r="AT240" t="n">
         <v>0</v>
       </c>
+      <c r="AU240" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV240" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -47537,6 +47957,11 @@
       <c r="Q245" t="n">
         <v>0</v>
       </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA245" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47549,13 +47974,23 @@
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR245" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS245" t="inlineStr"/>
       <c r="AT245" t="n">
         <v>0</v>
       </c>
+      <c r="AU245" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV245" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -48472,6 +48907,11 @@
       <c r="Q250" t="n">
         <v>0</v>
       </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48484,13 +48924,23 @@
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS250" t="inlineStr"/>
       <c r="AT250" t="n">
         <v>0</v>
       </c>
+      <c r="AU250" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV250" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -49407,6 +49857,11 @@
       <c r="Q255" t="n">
         <v>0</v>
       </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49419,13 +49874,23 @@
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS255" t="inlineStr"/>
       <c r="AT255" t="n">
         <v>0</v>
       </c>
+      <c r="AU255" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV255" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -50342,6 +50807,11 @@
       <c r="Q260" t="n">
         <v>0</v>
       </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA260" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50354,13 +50824,23 @@
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS260" t="inlineStr"/>
       <c r="AT260" t="n">
         <v>0</v>
       </c>
+      <c r="AU260" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV260" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -51277,6 +51757,11 @@
       <c r="Q265" t="n">
         <v>0</v>
       </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -51289,13 +51774,23 @@
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS265" t="inlineStr"/>
       <c r="AT265" t="n">
         <v>0</v>
       </c>
+      <c r="AU265" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV265" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -52212,6 +52707,11 @@
       <c r="Q270" t="n">
         <v>0</v>
       </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA270" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -52224,13 +52724,23 @@
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR270" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS270" t="inlineStr"/>
       <c r="AT270" t="n">
         <v>0</v>
       </c>
+      <c r="AU270" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV270" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -53147,6 +53657,11 @@
       <c r="Q275" t="n">
         <v>0</v>
       </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA275" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -53159,13 +53674,23 @@
       </c>
       <c r="AP275" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR275" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS275" t="inlineStr"/>
       <c r="AT275" t="n">
         <v>0</v>
       </c>
+      <c r="AU275" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV275" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -54082,6 +54607,11 @@
       <c r="Q280" t="n">
         <v>0</v>
       </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA280" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -54094,12 +54624,22 @@
       </c>
       <c r="AP280" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS280" t="inlineStr"/>
       <c r="AT280" t="n">
         <v>0</v>
+      </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV280" t="inlineStr">
         <is>
